--- a/InputData/trans/PVTStL/Policy Veh Types Subject to LCFS.xlsx
+++ b/InputData/trans/PVTStL/Policy Veh Types Subject to LCFS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\trans\PVTStL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\PVTStL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE39D9D-8C5C-4506-8739-69D1A3827F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8B7640-3F18-4F5C-A9FF-A8B089B6F820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="720" windowWidth="26730" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -585,10 +585,10 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">

--- a/InputData/trans/PVTStL/Policy Veh Types Subject to LCFS.xlsx
+++ b/InputData/trans/PVTStL/Policy Veh Types Subject to LCFS.xlsx
@@ -1,34 +1,89 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\PVTStL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\trans\PVTStL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8B7640-3F18-4F5C-A9FF-A8B089B6F820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{9AE39D9D-8C5C-4506-8739-69D1A3827F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E53B4F0-D340-48B1-B09D-53DD165E995F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="720" windowWidth="26730" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="PVTStL" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
+    <t>PVTStL Policy Vehicle Types Subject to LCFS</t>
+  </si>
+  <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>Emissions standards for ICEVs</t>
+  </si>
+  <si>
+    <t>Ministry of Road Transport and Highways/ Press Information Bureau</t>
+  </si>
+  <si>
+    <t>Bharat Stage VI Emissions Standards</t>
+  </si>
+  <si>
+    <t>https://www.transportpolicy.net/wp-content/uploads/2021/08/GSR-187E.pdf</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
+    <t>The LCFS percentage set (both the BAU LCFS and the user-specified</t>
+  </si>
+  <si>
+    <t>Additional LCFS Percentage policy lever) will only refer to the fuel</t>
+  </si>
+  <si>
+    <t>used by the vehicle types specified in this variable.  Other vehicle</t>
+  </si>
+  <si>
+    <t>types will be unaffected by the LCFS.</t>
+  </si>
+  <si>
+    <t>We exclude rail and aircraft as they are not regulated under the BS VI standards.</t>
+  </si>
+  <si>
+    <t>(Boolean)</t>
+  </si>
+  <si>
+    <t>passenger</t>
+  </si>
+  <si>
+    <t>freight</t>
+  </si>
+  <si>
     <t>LDVs</t>
   </si>
   <si>
@@ -45,52 +100,13 @@
   </si>
   <si>
     <t>motorbikes</t>
-  </si>
-  <si>
-    <t>passenger</t>
-  </si>
-  <si>
-    <t>freight</t>
-  </si>
-  <si>
-    <t>The LCFS percentage set (both the BAU LCFS and the user-specified</t>
-  </si>
-  <si>
-    <t>Additional LCFS Percentage policy lever) will only refer to the fuel</t>
-  </si>
-  <si>
-    <t>used by the vehicle types specified in this variable.  Other vehicle</t>
-  </si>
-  <si>
-    <t>types will be unaffected by the LCFS.</t>
-  </si>
-  <si>
-    <t>California Air Resources Board</t>
-  </si>
-  <si>
-    <t>Low Carbon Fuel Standard: Final Regulation Order</t>
-  </si>
-  <si>
-    <t>https://www.arb.ca.gov/regact/2015/lcfs2015/lcfsfinalregorder.pdf</t>
-  </si>
-  <si>
-    <t>Page 15</t>
-  </si>
-  <si>
-    <t>(Boolean)</t>
-  </si>
-  <si>
-    <t>Based on the California LCFS, we choose to exempt aircraft.</t>
-  </si>
-  <si>
-    <t>PVTStL Policy Vehicle Types Subject to LCFS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,6 +118,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -124,10 +155,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -136,8 +168,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -441,74 +476,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="B5" s="2">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="B6" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="B7" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="15" spans="1:2">
+      <c r="A15" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{1ED78FB6-6B48-46DC-B17D-7151329E646A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -518,27 +556,27 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="2" width="15.140625" customWidth="1"/>
     <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -547,9 +585,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -558,9 +596,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -569,31 +607,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
         <v>0</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -605,4 +643,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9312516-E4D1-451A-BB23-357D96114215}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31E3AB04-294F-4345-902B-53B8A603C416}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9E09A30-61B0-44D8-97CF-CF8AD635F91B}"/>
 </file>
--- a/InputData/trans/PVTStL/Policy Veh Types Subject to LCFS.xlsx
+++ b/InputData/trans/PVTStL/Policy Veh Types Subject to LCFS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\trans\PVTStL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\India EPS\InputData\trans\PVTStL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{9AE39D9D-8C5C-4506-8739-69D1A3827F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E53B4F0-D340-48B1-B09D-53DD165E995F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A14C4F-0EF0-456E-9744-E7A8C9F2BAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="720" windowWidth="26730" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5505" yWindow="2385" windowWidth="22020" windowHeight="12660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -106,7 +106,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -476,14 +476,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -491,52 +491,52 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>2016</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>11</v>
       </c>
@@ -556,14 +556,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -574,7 +574,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -596,7 +596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -607,7 +607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -618,7 +618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -646,6 +646,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
     <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
@@ -789,15 +798,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -805,13 +805,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9312516-E4D1-451A-BB23-357D96114215}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31E3AB04-294F-4345-902B-53B8A603C416}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31E3AB04-294F-4345-902B-53B8A603C416}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9312516-E4D1-451A-BB23-357D96114215}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9E09A30-61B0-44D8-97CF-CF8AD635F91B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9E09A30-61B0-44D8-97CF-CF8AD635F91B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>